--- a/research/traditional_assets/database/data/singapore/singapore_publishing_newspapers.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_publishing_newspapers.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.02268</v>
+        <v>0.912</v>
       </c>
       <c r="G2">
-        <v>-0.2524024318493822</v>
+        <v>-0.03687179487179487</v>
       </c>
       <c r="H2">
-        <v>-0.2524024318493822</v>
+        <v>-0.03687179487179487</v>
       </c>
       <c r="I2">
-        <v>-0.3210433418317317</v>
+        <v>-0.02794871794871795</v>
       </c>
       <c r="J2">
-        <v>-0.3210433418317317</v>
+        <v>-0.02033869426089848</v>
       </c>
       <c r="K2">
-        <v>-1.679</v>
+        <v>0.505</v>
       </c>
       <c r="L2">
-        <v>-0.3292802510296137</v>
+        <v>0.0258974358974359</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,73 +624,76 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.185</v>
+        <v>7.02</v>
       </c>
       <c r="V2">
-        <v>0.1473848777714611</v>
+        <v>2.127272727272727</v>
       </c>
       <c r="W2">
-        <v>-0.2583398412078615</v>
+        <v>0.5080482897384306</v>
       </c>
       <c r="X2">
-        <v>0.09183211049430809</v>
+        <v>0.08559337454183516</v>
       </c>
       <c r="Y2">
-        <v>-0.3501719517021696</v>
+        <v>0.4224549151965955</v>
       </c>
       <c r="Z2">
-        <v>0.5735658042744657</v>
+        <v>240.7407407407407</v>
+      </c>
+      <c r="AA2">
+        <v>-4.89635232206815</v>
       </c>
       <c r="AB2">
-        <v>0.09041316745655123</v>
+        <v>0.08456024592933256</v>
+      </c>
+      <c r="AC2">
+        <v>-4.980912567997483</v>
       </c>
       <c r="AD2">
-        <v>2.16</v>
+        <v>0.152</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.16</v>
+        <v>0.152</v>
       </c>
       <c r="AG2">
-        <v>-3.024999999999999</v>
+        <v>-6.867999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.0578468130690948</v>
+        <v>0.0440324449594438</v>
       </c>
       <c r="AI2">
-        <v>0.1536928988188416</v>
+        <v>0.06462585034013604</v>
       </c>
       <c r="AJ2">
-        <v>-0.09407557145078524</v>
+        <v>1.924887892376682</v>
       </c>
       <c r="AK2">
-        <v>-0.3410756567820498</v>
+        <v>1.471293916023993</v>
       </c>
       <c r="AL2">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.04099999999999999</v>
+        <v>-0.081</v>
       </c>
       <c r="AN2">
-        <v>-1.489655172413793</v>
-      </c>
-      <c r="AO2">
-        <v>-109.1333333333333</v>
+        <v>-0.3064516129032258</v>
       </c>
       <c r="AP2">
-        <v>2.086206896551724</v>
+        <v>13.84677419354839</v>
       </c>
       <c r="AQ2">
-        <v>39.92682926829269</v>
+        <v>6.728395061728396</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A-Smart Holdings Ltd. (SGX:BQC)</t>
+          <t>Bacui Technologies International Ltd. (Catalist:YYB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,25 +713,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0484</v>
+        <v>0.912</v>
       </c>
       <c r="G3">
-        <v>-0.190561797752809</v>
+        <v>-0.03687179487179487</v>
       </c>
       <c r="H3">
-        <v>-0.190561797752809</v>
+        <v>-0.03687179487179487</v>
       </c>
       <c r="I3">
-        <v>-0.2269662921348315</v>
+        <v>-0.02794871794871795</v>
       </c>
       <c r="J3">
-        <v>-0.2269662921348315</v>
+        <v>-0.02033869426089848</v>
       </c>
       <c r="K3">
-        <v>-0.795</v>
+        <v>0.505</v>
       </c>
       <c r="L3">
-        <v>-0.1786516853932584</v>
+        <v>0.0258974358974359</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,7 +740,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,195 +749,76 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.34</v>
+        <v>7.02</v>
       </c>
       <c r="V3">
-        <v>0.1369085173501577</v>
+        <v>2.127272727272727</v>
       </c>
       <c r="W3">
-        <v>-0.06794871794871796</v>
+        <v>0.5080482897384306</v>
       </c>
       <c r="X3">
-        <v>0.09329049190597005</v>
+        <v>0.08559337454183516</v>
       </c>
       <c r="Y3">
-        <v>-0.161239209854688</v>
+        <v>0.4224549151965955</v>
       </c>
       <c r="Z3">
-        <v>0.5005624296962879</v>
+        <v>240.7407407407407</v>
       </c>
       <c r="AA3">
-        <v>-0.1136107986501687</v>
+        <v>-4.89635232206815</v>
       </c>
       <c r="AB3">
-        <v>0.09045260583045631</v>
+        <v>0.08456024592933256</v>
       </c>
       <c r="AC3">
-        <v>-0.204063404480625</v>
+        <v>-4.980912567997483</v>
       </c>
       <c r="AD3">
-        <v>2.16</v>
+        <v>0.152</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.16</v>
+        <v>0.152</v>
       </c>
       <c r="AG3">
-        <v>-2.18</v>
+        <v>-6.867999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.06379208505611342</v>
+        <v>0.0440324449594438</v>
       </c>
       <c r="AI3">
-        <v>0.1653905053598775</v>
+        <v>0.06462585034013604</v>
       </c>
       <c r="AJ3">
-        <v>-0.07384823848238481</v>
+        <v>1.924887892376682</v>
       </c>
       <c r="AK3">
-        <v>-0.2499999999999999</v>
+        <v>1.471293916023993</v>
       </c>
       <c r="AL3">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.037</v>
+        <v>-0.081</v>
       </c>
       <c r="AN3">
-        <v>-2.547169811320755</v>
-      </c>
-      <c r="AO3">
-        <v>-67.33333333333334</v>
+        <v>-0.3064516129032258</v>
       </c>
       <c r="AP3">
-        <v>2.570754716981132</v>
+        <v>13.84677419354839</v>
       </c>
       <c r="AQ3">
-        <v>27.2972972972973</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Arion Entertainment Singapore Limited (Catalist:YYB)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Publishing &amp; Newspapers</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.00304</v>
-      </c>
-      <c r="G4">
-        <v>-0.6764252696456086</v>
-      </c>
-      <c r="H4">
-        <v>-0.6764252696456086</v>
-      </c>
-      <c r="I4">
-        <v>-0.9661016949152542</v>
-      </c>
-      <c r="J4">
-        <v>-0.9661016949152542</v>
-      </c>
-      <c r="K4">
-        <v>-0.884</v>
-      </c>
-      <c r="L4">
-        <v>-1.362095531587057</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0.845</v>
-      </c>
-      <c r="V4">
-        <v>0.242816091954023</v>
-      </c>
-      <c r="W4">
-        <v>-0.4487309644670051</v>
-      </c>
-      <c r="X4">
-        <v>0.09037372908264614</v>
-      </c>
-      <c r="Y4">
-        <v>-0.5391046935496513</v>
-      </c>
-      <c r="AB4">
-        <v>0.09037372908264614</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>-0.845</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.3206831119544592</v>
-      </c>
-      <c r="AK4">
-        <v>-5.671140939597314</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>-0.004</v>
-      </c>
-      <c r="AN4">
-        <v>-0</v>
-      </c>
-      <c r="AP4">
-        <v>1.403654485049834</v>
-      </c>
-      <c r="AQ4">
-        <v>156.75</v>
+        <v>6.728395061728396</v>
       </c>
     </row>
   </sheetData>
